--- a/models/6594_DCF_Model_20260906.xlsx
+++ b/models/6594_DCF_Model_20260906.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ryosuke0923\ryosuke-japanese-equity-research\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73DCD414-2620-46E1-A5EB-534108531432}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{262C57C4-E5CC-4D85-98BE-2A718D82A457}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="350">
   <si>
     <t>DISCLAIMER: This is a sample analysis for demonstration purposes only. It does not constitute investment advice.</t>
   </si>
@@ -80,7 +80,7 @@
     <t>vs Current Price</t>
   </si>
   <si>
-    <t>DCF - Perpetuity Growth [参考・Target不算入 — 追補6 §X]</t>
+    <t>DCF - Perpetuity Growth</t>
   </si>
   <si>
     <t>DCF - Exit Multiple</t>
@@ -92,7 +92,7 @@
     <t>Comps - PER Median [参考・Target不算入]</t>
   </si>
   <si>
-    <t>Note: Target Mid は DCF 2法（PGM / Exit）の平均のみ。Comps 2法は [参考] で Target 不算入（EV&lt;ネットデットで株式価値が負になる手法は INVALID として平均から除外） ■【追補6 §X】PGMとExitの乖離が **3.12倍** で 3.0倍を超えたため、**乖離そのものを裁定トリガーとする追補6 §X により中点平均を禁止**し、どちらの脚を落とすかを判定した。■**観測倍率バンドテスト**: Peer の実測 EV/EBITDA の第1〜第3四分位バンドは **14.33-21.37倍**。これに対し **PGM逆算 4.99倍 / 仮定Exit 15.60倍**。**PGM法のみがバンドの外にあるため PGM法を[参考]に降格し、Target = Exit 単独**とした。■バンドテストは市場倍率を無条件のアンカーにするものではない（それではスクリーナーが市場の複写に堕する）。**実際に取引されているレンジの外に出た脚だけを取り除く**という位置づけである。</t>
+    <t>Note: Target Mid は DCF 2法（PGM / Exit）の平均のみ。Comps 2法は [参考] で Target 不算入（EV&lt;ネットデットで株式価値が負になる手法は INVALID として平均から除外）</t>
   </si>
   <si>
     <t>DCF Valuation Range (PGM - Exit)</t>
@@ -614,7 +614,7 @@
     <t>Comparable Company Analysis</t>
   </si>
   <si>
-    <t>Peer prices as of 2026-09-06 (Mkt Cap / EV of peer rows are static CSV values; the subject row is live-linked to Executive Summary)</t>
+    <t>Peer prices as of 2026-09-07 (Mkt Cap / EV of peer rows are static CSV values; the subject row is live-linked to Executive Summary)</t>
   </si>
   <si>
     <t>Mkt Cap
@@ -783,13 +783,13 @@
     <t>状態</t>
   </si>
   <si>
-    <t>2026-09-06</t>
+    <t>2026-09-07</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>Generated by pipeline on 2026-09-06 22:47, template rev 034a4bb</t>
+    <t>Generated by pipeline on 2026-09-07 11:45, template rev a5a93a8</t>
   </si>
   <si>
     <t>初期生成（手修正なし）</t>
@@ -813,21 +813,6 @@
     <t>確定</t>
   </si>
   <si>
-    <t>Executive Summary!C10</t>
-  </si>
-  <si>
-    <t>PGM法を[参考]に降格 → Target = Exit 単独（C10 は C17 を参照）</t>
-  </si>
-  <si>
-    <t>【追補6 §X】PGMとExitの乖離が **3.12倍** で 3.0倍を超えたため、**乖離そのものを裁定トリガーとする追補6 §X により中点平均を禁止**し、どちらの脚を落とすかを判定した。■**観測倍率バンドテスト**: Peer の実測 EV/EBITDA の第1〜第3四分位バンドは **14.33-21.37倍**。これに対し **PGM逆算 4.99倍 / 仮定Exit 15.60倍**。**PGM法のみがバンドの外にあるため PGM法を[参考]に降格し、Target = Exit 単独**とした。■バンドテストは市場倍率を無条件のアンカーにするものではない（それではスクリーナーが市場の複写に堕する）。**実際に取引されているレンジの外に出た脚だけを取り除く**という位置づけである。</t>
-  </si>
-  <si>
-    <t>PGM/Exit の中点平均</t>
-  </si>
-  <si>
-    <t>裁定適用（追補6 §X）</t>
-  </si>
-  <si>
     <t>Pipeline Metadata (do not edit — read by scripts/validate_output.py)</t>
   </si>
   <si>
@@ -885,7 +870,7 @@
     <t>capex_pct_c5</t>
   </si>
   <si>
-    <t>0.0556</t>
+    <t>0.046288</t>
   </si>
   <si>
     <t>capex_pct_hist3yr</t>
@@ -978,7 +963,7 @@
     <t>da_pct_c18</t>
   </si>
   <si>
-    <t>0.0529</t>
+    <t>0.052944</t>
   </si>
   <si>
     <t>da_pct_hist3yr</t>
@@ -1020,7 +1005,7 @@
     <t>generated_at</t>
   </si>
   <si>
-    <t>2026-09-06 22:47:38</t>
+    <t>2026-09-07 11:45:11</t>
   </si>
   <si>
     <t>guidance_note</t>
@@ -1095,7 +1080,7 @@
     <t>template_rev</t>
   </si>
   <si>
-    <t>034a4bb</t>
+    <t>a5a93a8</t>
   </si>
   <si>
     <t>ticker</t>
@@ -1660,7 +1645,7 @@
     <col min="3" max="5" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:5" ht="14" x14ac:dyDescent="0.3">
       <c r="B1" s="45" t="s">
         <v>0</v>
       </c>
@@ -1668,19 +1653,19 @@
       <c r="D1" s="44"/>
       <c r="E1" s="44"/>
     </row>
-    <row r="3" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:5" ht="18" x14ac:dyDescent="0.4">
       <c r="B3" s="43" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="44"/>
       <c r="D3" s="44"/>
     </row>
-    <row r="4" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:5" ht="14" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:5" ht="14" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
@@ -1688,7 +1673,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:5" ht="14" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
         <v>5</v>
       </c>
@@ -1696,7 +1681,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:5" ht="14" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
         <v>7</v>
       </c>
@@ -1704,7 +1689,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:5" ht="14" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
         <v>9</v>
       </c>
@@ -1712,41 +1697,41 @@
         <v>2611</v>
       </c>
     </row>
-    <row r="10" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:5" ht="14" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C10" s="5">
-        <f>IF(ISNUMBER(C17),ROUND(C17,0),"N/A")</f>
-        <v>4053</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+        <f>IF(COUNT(C16:C17)=0,"N/A",ROUND(AVERAGE(C16:C17),0))</f>
+        <v>2993</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" ht="14" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C11" s="6" t="str">
         <f>IF(NOT(ISNUMBER(C12)),"N/A",IF(C12&gt;0.15,"BUY",IF(C12&gt;0.05,"HOLD","SELL")))</f>
-        <v>BUY</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+        <v>HOLD</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" ht="14" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C12" s="7">
         <f>IF(ISNUMBER(C10),(C10-C9)/C9,"N/A")</f>
-        <v>0.55227882037533516</v>
-      </c>
-    </row>
-    <row r="14" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0.14630409804672539</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" ht="14" x14ac:dyDescent="0.3">
       <c r="B14" s="8" t="s">
         <v>13</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
     </row>
-    <row r="15" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:5" ht="14" x14ac:dyDescent="0.3">
       <c r="B15" s="10" t="s">
         <v>14</v>
       </c>
@@ -1757,33 +1742,33 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:5" ht="13.5" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>17</v>
       </c>
       <c r="C16" s="11">
         <f>IF('DCF Model'!C53&lt;'DCF Model'!C16,"INVALID (EV &lt; net debt)",'DCF Model'!C55)</f>
-        <v>1575</v>
+        <v>1842</v>
       </c>
       <c r="D16" s="7">
         <f>IF(ISNUMBER(C16),(C16-C9)/C9,"N/A")</f>
-        <v>-0.39678284182305629</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>-0.29452317119877441</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" ht="13.5" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>18</v>
       </c>
       <c r="C17" s="11">
         <f>IF('DCF Model'!C62&lt;'DCF Model'!C16,"INVALID (EV &lt; net debt)",'DCF Model'!C64)</f>
-        <v>4053</v>
+        <v>4143</v>
       </c>
       <c r="D17" s="7">
         <f>IF(ISNUMBER(C17),(C17-C9)/C9,"N/A")</f>
-        <v>0.55227882037533516</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.5867483722711605</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" ht="13.5" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>19</v>
       </c>
@@ -1796,7 +1781,7 @@
         <v>0.83186518575258517</v>
       </c>
     </row>
-    <row r="19" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:5" ht="13.5" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>20</v>
       </c>
@@ -1809,7 +1794,7 @@
         <v>0.64726158559938718</v>
       </c>
     </row>
-    <row r="20" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:5" ht="14" x14ac:dyDescent="0.3">
       <c r="B20" s="45" t="s">
         <v>21</v>
       </c>
@@ -1817,16 +1802,16 @@
       <c r="D20" s="44"/>
       <c r="E20" s="44"/>
     </row>
-    <row r="21" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:5" ht="14" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
         <v>22</v>
       </c>
       <c r="C21" s="6" t="str">
         <f>IF(COUNT(C16:C17)=0,"N/A",MIN(C16:C17)&amp;" - "&amp;MAX(C16:C17))</f>
-        <v>1575 - 4053</v>
-      </c>
-    </row>
-    <row r="23" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1842 - 4143</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" ht="14" x14ac:dyDescent="0.3">
       <c r="B23" s="8" t="s">
         <v>23</v>
       </c>
@@ -1849,7 +1834,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:5" ht="14" x14ac:dyDescent="0.3">
       <c r="B28" s="8" t="s">
         <v>26</v>
       </c>
@@ -1895,12 +1880,12 @@
     <col min="3" max="6" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:6" ht="18" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:6" ht="14" x14ac:dyDescent="0.3">
       <c r="C4" s="10" t="s">
         <v>31</v>
       </c>
@@ -1914,12 +1899,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:6" ht="14" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:6" ht="14" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>36</v>
       </c>
@@ -1936,7 +1921,7 @@
         <v>2607813</v>
       </c>
     </row>
-    <row r="7" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:6" ht="14" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
         <v>37</v>
       </c>
@@ -1953,7 +1938,7 @@
         <v>2071392</v>
       </c>
     </row>
-    <row r="8" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:6" ht="14" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
         <v>38</v>
       </c>
@@ -1974,7 +1959,7 @@
         <v>536421</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:6" ht="13.5" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>39</v>
       </c>
@@ -1995,7 +1980,7 @@
         <v>0.20569764779913283</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:6" ht="14" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
         <v>40</v>
       </c>
@@ -2012,7 +1997,7 @@
         <v>217706</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:6" ht="14" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
         <v>41</v>
       </c>
@@ -2029,7 +2014,7 @@
         <v>238116</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:6" ht="14" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
         <v>42</v>
       </c>
@@ -2046,7 +2031,7 @@
         <v>164365</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:6" ht="13.5" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>43</v>
       </c>
@@ -2067,7 +2052,7 @@
         <v>9.1308694296715287E-2</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:6" ht="13.5" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>44</v>
       </c>
@@ -2088,7 +2073,7 @@
         <v>6.3027908826284701E-2</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:6" ht="13.5" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>45</v>
       </c>
@@ -2108,7 +2093,7 @@
         <v>0.11105084913293049</v>
       </c>
     </row>
-    <row r="16" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:6" ht="13.5" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>47</v>
       </c>
@@ -2128,12 +2113,12 @@
         <v>0.47115954922894426</v>
       </c>
     </row>
-    <row r="18" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:6" ht="14" x14ac:dyDescent="0.3">
       <c r="B18" s="3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:6" ht="14" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
         <v>49</v>
       </c>
@@ -2150,7 +2135,7 @@
         <v>284428</v>
       </c>
     </row>
-    <row r="20" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:6" ht="14" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
         <v>50</v>
       </c>
@@ -2159,7 +2144,7 @@
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
     </row>
-    <row r="21" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:6" ht="14" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
         <v>51</v>
       </c>
@@ -2174,12 +2159,12 @@
         <v>53</v>
       </c>
     </row>
-    <row r="25" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:6" ht="14" x14ac:dyDescent="0.3">
       <c r="B25" s="3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="26" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:6" ht="14" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
         <v>55</v>
       </c>
@@ -2196,7 +2181,7 @@
         <v>246239</v>
       </c>
     </row>
-    <row r="27" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:6" ht="14" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
         <v>56</v>
       </c>
@@ -2205,12 +2190,12 @@
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
     </row>
-    <row r="28" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:6" ht="14" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:6" ht="14" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
         <v>58</v>
       </c>
@@ -2234,12 +2219,12 @@
     <col min="3" max="7" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:7" ht="18" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B4" s="8" t="s">
         <v>60</v>
       </c>
@@ -2249,15 +2234,15 @@
       <c r="F4" s="9"/>
       <c r="G4" s="9"/>
     </row>
-    <row r="5" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>53</v>
       </c>
       <c r="C5" s="7">
-        <v>5.5599999999999997E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+        <v>4.6288000000000003E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>61</v>
       </c>
@@ -2265,7 +2250,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="7" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
         <v>62</v>
       </c>
@@ -2273,7 +2258,7 @@
         <v>2.9700000000000001E-2</v>
       </c>
     </row>
-    <row r="8" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
         <v>63</v>
       </c>
@@ -2281,7 +2266,7 @@
         <v>1.0367999999999999</v>
       </c>
     </row>
-    <row r="9" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
         <v>64</v>
       </c>
@@ -2289,7 +2274,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="10" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
         <v>65</v>
       </c>
@@ -2297,7 +2282,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="11" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
         <v>66</v>
       </c>
@@ -2305,7 +2290,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="12" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
         <v>67</v>
       </c>
@@ -2313,7 +2298,7 @@
         <v>0.12280000000000001</v>
       </c>
     </row>
-    <row r="13" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
         <v>68</v>
       </c>
@@ -2321,7 +2306,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="14" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
         <v>69</v>
       </c>
@@ -2329,7 +2314,7 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="15" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
         <v>70</v>
       </c>
@@ -2337,7 +2322,7 @@
         <v>1146309835</v>
       </c>
     </row>
-    <row r="16" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
         <v>71</v>
       </c>
@@ -2345,7 +2330,7 @@
         <v>367577</v>
       </c>
     </row>
-    <row r="17" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
         <v>72</v>
       </c>
@@ -2353,15 +2338,15 @@
         <v>2607813</v>
       </c>
     </row>
-    <row r="18" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
         <v>73</v>
       </c>
       <c r="C18" s="7">
-        <v>5.2900000000000003E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+        <v>5.2943999999999998E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
         <v>74</v>
       </c>
@@ -2369,7 +2354,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="20" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
         <v>75</v>
       </c>
@@ -2377,7 +2362,7 @@
         <v>2616305</v>
       </c>
     </row>
-    <row r="22" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B22" s="8" t="s">
         <v>76</v>
       </c>
@@ -2387,7 +2372,7 @@
       <c r="F22" s="9"/>
       <c r="G22" s="9"/>
     </row>
-    <row r="23" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
         <v>77</v>
       </c>
@@ -2396,7 +2381,7 @@
         <v>0.10709199999999999</v>
       </c>
     </row>
-    <row r="24" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
         <v>78</v>
       </c>
@@ -2405,7 +2390,7 @@
         <v>0.89063056644104022</v>
       </c>
     </row>
-    <row r="25" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
         <v>79</v>
       </c>
@@ -2414,7 +2399,7 @@
         <v>0.10936943355895974</v>
       </c>
     </row>
-    <row r="26" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
         <v>80</v>
       </c>
@@ -2423,7 +2408,7 @@
         <v>9.6473102956893472E-2</v>
       </c>
     </row>
-    <row r="27" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
         <v>81</v>
       </c>
@@ -2435,7 +2420,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B28" s="8" t="s">
         <v>83</v>
       </c>
@@ -2445,7 +2430,7 @@
       <c r="F28" s="9"/>
       <c r="G28" s="9"/>
     </row>
-    <row r="29" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="C29" s="10" t="s">
         <v>84</v>
       </c>
@@ -2462,7 +2447,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="30" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B30" s="4" t="s">
         <v>45</v>
       </c>
@@ -2487,7 +2472,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="31" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B31" s="4" t="s">
         <v>89</v>
       </c>
@@ -2512,7 +2497,7 @@
         <v>0.79430000000000001</v>
       </c>
     </row>
-    <row r="32" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
         <v>90</v>
       </c>
@@ -2537,7 +2522,7 @@
         <v>0.1153</v>
       </c>
     </row>
-    <row r="33" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B33" s="4" t="s">
         <v>36</v>
       </c>
@@ -2562,7 +2547,7 @@
         <v>2828606.1028641891</v>
       </c>
     </row>
-    <row r="34" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B34" s="4" t="s">
         <v>37</v>
       </c>
@@ -2587,7 +2572,7 @@
         <v>2246761.8275050255</v>
       </c>
     </row>
-    <row r="35" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B35" s="4" t="s">
         <v>38</v>
       </c>
@@ -2612,7 +2597,7 @@
         <v>581844.27535916353</v>
       </c>
     </row>
-    <row r="36" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B36" s="4" t="s">
         <v>39</v>
       </c>
@@ -2637,7 +2622,7 @@
         <v>0.20569999999999994</v>
       </c>
     </row>
-    <row r="37" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B37" s="4" t="s">
         <v>91</v>
       </c>
@@ -2662,7 +2647,7 @@
         <v>326138.283660241</v>
       </c>
     </row>
-    <row r="38" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B38" s="4" t="s">
         <v>92</v>
       </c>
@@ -2687,7 +2672,7 @@
         <v>9.0399999999999939E-2</v>
       </c>
     </row>
-    <row r="39" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B39" s="4" t="s">
         <v>93</v>
       </c>
@@ -2712,7 +2697,7 @@
         <v>255705.99169892253</v>
       </c>
     </row>
-    <row r="40" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B40" s="4" t="s">
         <v>94</v>
       </c>
@@ -2737,7 +2722,7 @@
         <v>63926.497924730633</v>
       </c>
     </row>
-    <row r="41" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B41" s="4" t="s">
         <v>95</v>
       </c>
@@ -2762,57 +2747,57 @@
         <v>191779.49377419188</v>
       </c>
     </row>
-    <row r="42" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B42" s="4" t="s">
         <v>96</v>
       </c>
       <c r="C42" s="5">
         <f>C33*C18</f>
-        <v>138918.98085389999</v>
+        <v>139034.52783230398</v>
       </c>
       <c r="D42" s="5">
         <f>D33*C18</f>
-        <v>141002.76556670849</v>
+        <v>141120.04574978852</v>
       </c>
       <c r="E42" s="5">
         <f>E33*C18</f>
-        <v>143822.82087804266</v>
+        <v>143942.44666478431</v>
       </c>
       <c r="F42" s="5">
         <f>F33*C18</f>
-        <v>146699.27729560353</v>
+        <v>146821.29559808</v>
       </c>
       <c r="G42" s="5">
         <f>G33*C18</f>
-        <v>149633.26284151562</v>
-      </c>
-    </row>
-    <row r="43" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+        <v>149757.72151004162</v>
+      </c>
+    </row>
+    <row r="43" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B43" s="4" t="s">
         <v>97</v>
       </c>
       <c r="C43" s="5">
         <f>C33*C5</f>
-        <v>146009.36361959996</v>
+        <v>121555.42128100799</v>
       </c>
       <c r="D43" s="5">
         <f>D33*C5</f>
-        <v>148199.50407389397</v>
+        <v>123378.7526002231</v>
       </c>
       <c r="E43" s="5">
         <f>E33*C5</f>
-        <v>151163.49415537185</v>
+        <v>125846.32765222758</v>
       </c>
       <c r="F43" s="5">
         <f>F33*C5</f>
-        <v>154186.7640384793</v>
+        <v>128363.25420527214</v>
       </c>
       <c r="G43" s="5">
         <f>G33*C5</f>
-        <v>157270.49931924889</v>
-      </c>
-    </row>
-    <row r="44" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+        <v>130930.5192893776</v>
+      </c>
+    </row>
+    <row r="44" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B44" s="4" t="s">
         <v>98</v>
       </c>
@@ -2837,32 +2822,32 @@
         <v>10891.098397921072</v>
       </c>
     </row>
-    <row r="45" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B45" s="4" t="s">
         <v>99</v>
       </c>
       <c r="C45" s="20">
         <f>C41+C42-C43-C44</f>
-        <v>337108.92917313281</v>
+        <v>361678.41849012871</v>
       </c>
       <c r="D45" s="20">
         <f>D41+D42-D43-D44</f>
-        <v>165786.25062169702</v>
+        <v>190724.28227844794</v>
       </c>
       <c r="E45" s="20">
         <f>E41+E42-E43-E44</f>
-        <v>166523.60524657607</v>
+        <v>191960.39753646194</v>
       </c>
       <c r="F45" s="20">
         <f>F41+F42-F43-F44</f>
-        <v>169854.07735150761</v>
+        <v>195799.60548719129</v>
       </c>
       <c r="G45" s="20">
         <f>G41+G42-G43-G44</f>
-        <v>173251.15889853757</v>
-      </c>
-    </row>
-    <row r="46" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+        <v>199715.59759693482</v>
+      </c>
+    </row>
+    <row r="46" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B46" s="4" t="s">
         <v>100</v>
       </c>
@@ -2887,32 +2872,32 @@
         <v>0.66070725845101452</v>
       </c>
     </row>
-    <row r="47" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B47" s="4" t="s">
         <v>101</v>
       </c>
       <c r="C47" s="19">
         <f>C45*C46</f>
-        <v>321937.27574877493</v>
+        <v>345401.01038390811</v>
       </c>
       <c r="D47" s="19">
         <f>D45*D46</f>
-        <v>144394.79408529418</v>
+        <v>166115.06300063347</v>
       </c>
       <c r="E47" s="19">
         <f>E45*E46</f>
-        <v>132275.93745800119</v>
+        <v>152481.33441110549</v>
       </c>
       <c r="F47" s="19">
         <f>F45*F46</f>
-        <v>123050.40209679044</v>
+        <v>141846.58126122973</v>
       </c>
       <c r="G47" s="19">
         <f>G45*G46</f>
-        <v>114468.29821931385</v>
-      </c>
-    </row>
-    <row r="49" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+        <v>131953.54495817682</v>
+      </c>
+    </row>
+    <row r="49" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B49" s="22" t="s">
         <v>102</v>
       </c>
@@ -2922,61 +2907,61 @@
       <c r="F49" s="23"/>
       <c r="G49" s="23"/>
     </row>
-    <row r="50" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B50" s="4" t="s">
         <v>103</v>
       </c>
       <c r="C50" s="5">
         <f>SUM(C47:G47)</f>
-        <v>836126.70760817453</v>
-      </c>
-    </row>
-    <row r="51" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+        <v>937797.53401505353</v>
+      </c>
+    </row>
+    <row r="51" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B51" s="4" t="s">
         <v>104</v>
       </c>
       <c r="C51" s="5">
         <f>G45*(1+C13)/(C26-C13)</f>
-        <v>2023561.8302578048</v>
-      </c>
-    </row>
-    <row r="52" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+        <v>2332664.6861910028</v>
+      </c>
+    </row>
+    <row r="52" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B52" s="4" t="s">
         <v>105</v>
       </c>
       <c r="C52" s="5">
         <f>C51*G46</f>
-        <v>1336981.9891757513</v>
-      </c>
-    </row>
-    <row r="53" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1541208.4896987537</v>
+      </c>
+    </row>
+    <row r="53" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B53" s="4" t="s">
         <v>106</v>
       </c>
       <c r="C53" s="5">
         <f>C50+C52</f>
-        <v>2173108.6967839259</v>
-      </c>
-    </row>
-    <row r="54" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+        <v>2479006.0237138071</v>
+      </c>
+    </row>
+    <row r="54" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B54" s="4" t="s">
         <v>107</v>
       </c>
       <c r="C54" s="5">
         <f>C53-C16</f>
-        <v>1805531.6967839259</v>
-      </c>
-    </row>
-    <row r="55" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+        <v>2111429.0237138071</v>
+      </c>
+    </row>
+    <row r="55" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B55" s="4" t="s">
         <v>108</v>
       </c>
       <c r="C55" s="24">
         <f>ROUND(C54*1000000/C15,0)</f>
-        <v>1575</v>
-      </c>
-    </row>
-    <row r="57" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1842</v>
+      </c>
+    </row>
+    <row r="57" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B57" s="22" t="s">
         <v>109</v>
       </c>
@@ -2986,70 +2971,70 @@
       <c r="F57" s="23"/>
       <c r="G57" s="23"/>
     </row>
-    <row r="58" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B58" s="4" t="s">
         <v>103</v>
       </c>
       <c r="C58" s="5">
         <f>C50</f>
-        <v>836126.70760817453</v>
-      </c>
-    </row>
-    <row r="59" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+        <v>937797.53401505353</v>
+      </c>
+    </row>
+    <row r="59" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B59" s="4" t="s">
         <v>110</v>
       </c>
       <c r="C59" s="5">
         <f>G39+G42</f>
-        <v>405339.25454043818</v>
-      </c>
-    </row>
-    <row r="60" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+        <v>405463.71320896415</v>
+      </c>
+    </row>
+    <row r="60" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B60" s="4" t="s">
         <v>111</v>
       </c>
       <c r="C60" s="5">
         <f>C59*C14</f>
-        <v>6323292.3708308358</v>
-      </c>
-    </row>
-    <row r="61" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+        <v>6325233.9260598402</v>
+      </c>
+    </row>
+    <row r="61" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B61" s="4" t="s">
         <v>105</v>
       </c>
       <c r="C61" s="5">
         <f>C60*G46</f>
-        <v>4177845.1667158576</v>
-      </c>
-    </row>
-    <row r="62" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+        <v>4179127.966348344</v>
+      </c>
+    </row>
+    <row r="62" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B62" s="4" t="s">
         <v>106</v>
       </c>
       <c r="C62" s="5">
         <f>C58+C61</f>
-        <v>5013971.8743240321</v>
-      </c>
-    </row>
-    <row r="63" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+        <v>5116925.5003633974</v>
+      </c>
+    </row>
+    <row r="63" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B63" s="4" t="s">
         <v>107</v>
       </c>
       <c r="C63" s="5">
         <f>C62-C16</f>
-        <v>4646394.8743240321</v>
-      </c>
-    </row>
-    <row r="64" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+        <v>4749348.5003633974</v>
+      </c>
+    </row>
+    <row r="64" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B64" s="4" t="s">
         <v>112</v>
       </c>
       <c r="C64" s="24">
         <f>ROUND(C63*1000000/C15,0)</f>
-        <v>4053</v>
-      </c>
-    </row>
-    <row r="66" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+        <v>4143</v>
+      </c>
+    </row>
+    <row r="66" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B66" s="22" t="s">
         <v>113</v>
       </c>
@@ -3059,7 +3044,7 @@
       <c r="F66" s="23"/>
       <c r="G66" s="23"/>
     </row>
-    <row r="67" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="C67" s="25" t="s">
         <v>114</v>
       </c>
@@ -3076,12 +3061,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="68" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B68" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="69" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B69" s="4" t="s">
         <v>82</v>
       </c>
@@ -3101,7 +3086,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="70" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B70" s="4" t="s">
         <v>119</v>
       </c>
@@ -3121,7 +3106,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="71" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B71" s="4" t="s">
         <v>120</v>
       </c>
@@ -3141,7 +3126,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="72" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B72" s="4" t="s">
         <v>121</v>
       </c>
@@ -3161,7 +3146,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="73" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B73" s="4" t="s">
         <v>122</v>
       </c>
@@ -3181,12 +3166,12 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="75" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B75" s="3" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="76" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B76" s="4" t="s">
         <v>82</v>
       </c>
@@ -3206,7 +3191,7 @@
         <v>0.79430000000000001</v>
       </c>
     </row>
-    <row r="77" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B77" s="4" t="s">
         <v>119</v>
       </c>
@@ -3226,7 +3211,7 @@
         <v>0.79430000000000001</v>
       </c>
     </row>
-    <row r="78" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B78" s="4" t="s">
         <v>120</v>
       </c>
@@ -3246,7 +3231,7 @@
         <v>0.79430000000000001</v>
       </c>
     </row>
-    <row r="79" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B79" s="4" t="s">
         <v>121</v>
       </c>
@@ -3266,7 +3251,7 @@
         <v>0.79430000000000001</v>
       </c>
     </row>
-    <row r="80" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B80" s="4" t="s">
         <v>122</v>
       </c>
@@ -3286,12 +3271,12 @@
         <v>0.79430000000000001</v>
       </c>
     </row>
-    <row r="82" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B82" s="3" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="83" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B83" s="4" t="s">
         <v>82</v>
       </c>
@@ -3311,7 +3296,7 @@
         <v>0.1153</v>
       </c>
     </row>
-    <row r="84" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B84" s="4" t="s">
         <v>119</v>
       </c>
@@ -3331,7 +3316,7 @@
         <v>0.10440000000000001</v>
       </c>
     </row>
-    <row r="85" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B85" s="4" t="s">
         <v>120</v>
       </c>
@@ -3351,7 +3336,7 @@
         <v>0.1153</v>
       </c>
     </row>
-    <row r="86" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B86" s="4" t="s">
         <v>121</v>
       </c>
@@ -3371,7 +3356,7 @@
         <v>0.1439</v>
       </c>
     </row>
-    <row r="87" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B87" s="4" t="s">
         <v>122</v>
       </c>
@@ -3415,17 +3400,17 @@
     <col min="3" max="9" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:9" ht="18" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="3" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="5" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B5" s="8" t="s">
         <v>125</v>
       </c>
@@ -3437,7 +3422,7 @@
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
     </row>
-    <row r="6" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>126</v>
       </c>
@@ -3446,7 +3431,7 @@
         <v>2611</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
         <v>70</v>
       </c>
@@ -3455,7 +3440,7 @@
         <v>1146309835</v>
       </c>
     </row>
-    <row r="8" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
         <v>127</v>
       </c>
@@ -3464,7 +3449,7 @@
         <v>2993014.9791850001</v>
       </c>
     </row>
-    <row r="9" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
         <v>71</v>
       </c>
@@ -3473,7 +3458,7 @@
         <v>367577</v>
       </c>
     </row>
-    <row r="10" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
         <v>128</v>
       </c>
@@ -3482,7 +3467,7 @@
         <v>3360591.9791850001</v>
       </c>
     </row>
-    <row r="11" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
         <v>129</v>
       </c>
@@ -3491,7 +3476,7 @@
         <v>9.6473102956893472E-2</v>
       </c>
     </row>
-    <row r="12" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
         <v>130</v>
       </c>
@@ -3500,7 +3485,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="13" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
         <v>131</v>
       </c>
@@ -3509,7 +3494,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="14" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
         <v>132</v>
       </c>
@@ -3517,7 +3502,7 @@
         <v>238116</v>
       </c>
     </row>
-    <row r="15" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
         <v>133</v>
       </c>
@@ -3525,7 +3510,7 @@
         <v>238116</v>
       </c>
     </row>
-    <row r="16" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
         <v>134</v>
       </c>
@@ -3534,16 +3519,16 @@
         <v>2828606.1028641891</v>
       </c>
     </row>
-    <row r="17" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
         <v>135</v>
       </c>
       <c r="C17" s="5">
         <f>'DCF Model'!C53</f>
-        <v>2173108.6967839259</v>
-      </c>
-    </row>
-    <row r="18" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+        <v>2479006.0237138071</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
         <v>136</v>
       </c>
@@ -3551,25 +3536,25 @@
         <v>9.1308694296715287E-2</v>
       </c>
     </row>
-    <row r="19" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
         <v>137</v>
       </c>
       <c r="C19" s="5">
         <f>C10-C17</f>
-        <v>1187483.2824010742</v>
-      </c>
-    </row>
-    <row r="20" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+        <v>881585.95547119295</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
         <v>138</v>
       </c>
       <c r="C20" s="15">
         <f>IFERROR(ROUND(C19*1000000/C7,0),"N/A")</f>
-        <v>1036</v>
-      </c>
-    </row>
-    <row r="22" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B22" s="8" t="s">
         <v>139</v>
       </c>
@@ -3581,12 +3566,12 @@
       <c r="H22" s="9"/>
       <c r="I22" s="9"/>
     </row>
-    <row r="23" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="24" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
         <v>141</v>
       </c>
@@ -3595,7 +3580,7 @@
         <v>290600.81621217495</v>
       </c>
     </row>
-    <row r="25" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
         <v>142</v>
       </c>
@@ -3604,7 +3589,7 @@
         <v>387467.75494956662</v>
       </c>
     </row>
-    <row r="26" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
       <c r="B26" s="6" t="s">
         <v>143</v>
       </c>
@@ -3613,7 +3598,7 @@
         <v>1.6272226769707478</v>
       </c>
     </row>
-    <row r="27" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
       <c r="B27" s="6" t="s">
         <v>144</v>
       </c>
@@ -3622,7 +3607,7 @@
         <v>1.6272226769707478</v>
       </c>
     </row>
-    <row r="28" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
       <c r="B28" s="6" t="s">
         <v>145</v>
       </c>
@@ -3631,7 +3616,7 @@
         <v>0.13698187052528263</v>
       </c>
     </row>
-    <row r="29" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
       <c r="B29" s="6" t="s">
         <v>146</v>
       </c>
@@ -3640,7 +3625,7 @@
         <v>4243492.4508991176</v>
       </c>
     </row>
-    <row r="32" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B32" s="8" t="s">
         <v>147</v>
       </c>
@@ -3652,17 +3637,17 @@
       <c r="H32" s="9"/>
       <c r="I32" s="9"/>
     </row>
-    <row r="33" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B33" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="34" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B34" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="36" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B36" s="28" t="s">
         <v>150</v>
       </c>
@@ -3690,12 +3675,12 @@
         <v>0.11647310295689348</v>
       </c>
     </row>
-    <row r="37" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B37" s="3" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="38" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B38" s="4" t="s">
         <v>153</v>
       </c>
@@ -3723,7 +3708,7 @@
         <v>0.8645312450797249</v>
       </c>
     </row>
-    <row r="39" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B39" s="4" t="s">
         <v>154</v>
       </c>
@@ -3751,7 +3736,7 @@
         <v>1.6140213037280322</v>
       </c>
     </row>
-    <row r="40" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B40" s="4" t="s">
         <v>155</v>
       </c>
@@ -3779,7 +3764,7 @@
         <v>2.2656296849611919</v>
       </c>
     </row>
-    <row r="41" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B41" s="4" t="s">
         <v>156</v>
       </c>
@@ -3807,12 +3792,12 @@
         <v>3.0904566193454972</v>
       </c>
     </row>
-    <row r="42" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B42" s="3" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="43" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B43" s="4" t="s">
         <v>153</v>
       </c>
@@ -3840,7 +3825,7 @@
         <v>8.3680431028240161</v>
       </c>
     </row>
-    <row r="44" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B44" s="4" t="s">
         <v>154</v>
       </c>
@@ -3868,7 +3853,7 @@
         <v>7.4906208692971692</v>
       </c>
     </row>
-    <row r="45" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B45" s="4" t="s">
         <v>155</v>
       </c>
@@ -3896,7 +3881,7 @@
         <v>6.7363803790936974</v>
       </c>
     </row>
-    <row r="46" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B46" s="4" t="s">
         <v>156</v>
       </c>
@@ -3924,7 +3909,7 @@
         <v>5.7943742058055108</v>
       </c>
     </row>
-    <row r="47" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B47" s="22" t="s">
         <v>158</v>
       </c>
@@ -3936,7 +3921,7 @@
       <c r="H47" s="23"/>
       <c r="I47" s="23"/>
     </row>
-    <row r="48" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B48" s="4" t="s">
         <v>153</v>
       </c>
@@ -3964,7 +3949,7 @@
         <v>510863.83412436157</v>
       </c>
     </row>
-    <row r="49" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B49" s="4" t="s">
         <v>154</v>
       </c>
@@ -3992,7 +3977,7 @@
         <v>546879.23475238704</v>
       </c>
     </row>
-    <row r="50" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B50" s="4" t="s">
         <v>155</v>
       </c>
@@ -4020,7 +4005,7 @@
         <v>585077.80227903917</v>
       </c>
     </row>
-    <row r="51" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B51" s="4" t="s">
         <v>156</v>
       </c>
@@ -4048,7 +4033,7 @@
         <v>646299.67002404307</v>
       </c>
     </row>
-    <row r="52" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B52" s="22" t="s">
         <v>159</v>
       </c>
@@ -4060,7 +4045,7 @@
       <c r="H52" s="23"/>
       <c r="I52" s="23"/>
     </row>
-    <row r="53" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B53" s="4" t="s">
         <v>153</v>
       </c>
@@ -4088,7 +4073,7 @@
         <v>2.1454410208652992</v>
       </c>
     </row>
-    <row r="54" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B54" s="4" t="s">
         <v>154</v>
       </c>
@@ -4116,7 +4101,7 @@
         <v>2.2966925143727721</v>
       </c>
     </row>
-    <row r="55" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B55" s="4" t="s">
         <v>155</v>
       </c>
@@ -4144,7 +4129,7 @@
         <v>2.4571125093611483</v>
       </c>
     </row>
-    <row r="56" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B56" s="4" t="s">
         <v>156</v>
       </c>
@@ -4172,7 +4157,7 @@
         <v>2.7142219339483407</v>
       </c>
     </row>
-    <row r="58" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B58" s="8" t="s">
         <v>160</v>
       </c>
@@ -4184,12 +4169,12 @@
       <c r="H58" s="9"/>
       <c r="I58" s="9"/>
     </row>
-    <row r="59" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B59" s="1" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="60" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B60" s="4" t="s">
         <v>162</v>
       </c>
@@ -4198,7 +4183,7 @@
         <v>428689.69742827694</v>
       </c>
     </row>
-    <row r="62" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B62" s="28" t="s">
         <v>163</v>
       </c>
@@ -4209,7 +4194,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="63" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B63" s="31">
         <v>4.5699999999999998E-2</v>
       </c>
@@ -4222,7 +4207,7 @@
         <v>3.5970825144626302</v>
       </c>
     </row>
-    <row r="64" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B64" s="31">
         <v>6.8500000000000005E-2</v>
       </c>
@@ -4235,7 +4220,7 @@
         <v>2.3998054147582799</v>
       </c>
     </row>
-    <row r="65" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B65" s="4" t="s">
         <v>166</v>
       </c>
@@ -4248,7 +4233,7 @@
         <v>1.8003397395734726</v>
       </c>
     </row>
-    <row r="66" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B66" s="31">
         <v>0.11409999999999999</v>
       </c>
@@ -4261,7 +4246,7 @@
         <v>1.4407245478610187</v>
       </c>
     </row>
-    <row r="67" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B67" s="31">
         <v>0.13700000000000001</v>
       </c>
@@ -4274,7 +4259,7 @@
         <v>1.19990270737914</v>
       </c>
     </row>
-    <row r="69" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B69" s="8" t="s">
         <v>167</v>
       </c>
@@ -4286,7 +4271,7 @@
       <c r="H69" s="9"/>
       <c r="I69" s="9"/>
     </row>
-    <row r="70" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
       <c r="B70" s="6" t="s">
         <v>168</v>
       </c>
@@ -4295,7 +4280,7 @@
         <v>8.9333729748872894</v>
       </c>
     </row>
-    <row r="71" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
       <c r="B71" s="6" t="s">
         <v>169</v>
       </c>
@@ -4304,25 +4289,25 @@
         <v>1.2886629444615085</v>
       </c>
     </row>
-    <row r="72" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B72" s="4" t="s">
         <v>170</v>
       </c>
       <c r="C72" s="14">
         <f>IFERROR(C10/(C25+'DCF Model'!G42),"N/A")</f>
-        <v>6.2569086035360657</v>
-      </c>
-    </row>
-    <row r="73" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+        <v>6.2554590696848109</v>
+      </c>
+    </row>
+    <row r="73" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B73" s="4" t="s">
         <v>171</v>
       </c>
       <c r="C73" s="14">
         <f>IFERROR(C10/(C60+'DCF Model'!G42),"N/A")</f>
-        <v>5.8109260915687235</v>
-      </c>
-    </row>
-    <row r="74" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+        <v>5.8096758134957636</v>
+      </c>
+    </row>
+    <row r="74" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B74" s="4" t="s">
         <v>172</v>
       </c>
@@ -4331,12 +4316,12 @@
         <v>15.552094158010673</v>
       </c>
     </row>
-    <row r="75" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B75" s="1" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="77" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B77" s="22" t="s">
         <v>174</v>
       </c>
@@ -4348,16 +4333,16 @@
       <c r="H77" s="23"/>
       <c r="I77" s="23"/>
     </row>
-    <row r="78" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B78" s="4" t="str">
         <f>"At "&amp;TEXT(C6,"#,##0")&amp;" yen the market is paying for a steady-state operating profit of "&amp;TEXT(F49,"#,##0")&amp;" mn JPY - "&amp;TEXT(F54,"0.00")&amp;"x the FY2025 cycle peak of "&amp;TEXT(C15,"#,##0")&amp;" mn - reached in 5 years and sustained for ever, against "&amp;TEXT(C14,"#,##0")&amp;" mn actually earned in FY2025."</f>
         <v>At 2,611 yen the market is paying for a steady-state operating profit of 428,690 mn JPY - 1.80x the FY2025 cycle peak of 238,116 mn - reached in 5 years and sustained for ever, against 238,116 mn actually earned in FY2025.</v>
       </c>
     </row>
-    <row r="79" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B79" s="4" t="str">
         <f>"Even with no ramp at all (Block A) the price needs "&amp;TEXT(C25,"#,##0")&amp;" mn, or "&amp;TEXT(C26,"0.00")&amp;"x the peak. The base case supports an EV of only "&amp;TEXT(C17,"#,##0")&amp;" mn, leaving "&amp;TEXT(C20,"#,##0")&amp;" yen per share of the current price unexplained by mid-cycle economics."</f>
-        <v>Even with no ramp at all (Block A) the price needs 387,468 mn, or 1.63x the peak. The base case supports an EV of only 2,173,109 mn, leaving 1,036 yen per share of the current price unexplained by mid-cycle economics.</v>
+        <v>Even with no ramp at all (Block A) the price needs 387,468 mn, or 1.63x the peak. The base case supports an EV of only 2,479,006 mn, leaving 769 yen per share of the current price unexplained by mid-cycle economics.</v>
       </c>
     </row>
   </sheetData>
@@ -4379,12 +4364,12 @@
     <col min="3" max="8" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:8" ht="18" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:8" ht="14" x14ac:dyDescent="0.3">
       <c r="B4" s="8" t="s">
         <v>176</v>
       </c>
@@ -4407,7 +4392,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:8" ht="14" x14ac:dyDescent="0.3">
       <c r="B5" s="33" t="s">
         <v>178</v>
       </c>
@@ -4436,7 +4421,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:8" ht="14" x14ac:dyDescent="0.3">
       <c r="B6" s="33" t="s">
         <v>179</v>
       </c>
@@ -4465,7 +4450,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:8" ht="14" x14ac:dyDescent="0.3">
       <c r="B7" s="33" t="s">
         <v>180</v>
       </c>
@@ -4494,7 +4479,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:8" ht="14" x14ac:dyDescent="0.3">
       <c r="B8" s="8" t="s">
         <v>181</v>
       </c>
@@ -4505,7 +4490,7 @@
       <c r="G8" s="9"/>
       <c r="H8" s="9"/>
     </row>
-    <row r="9" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:8" ht="14" x14ac:dyDescent="0.3">
       <c r="B9" s="33" t="s">
         <v>36</v>
       </c>
@@ -4533,7 +4518,7 @@
         <v>2828606.1028641891</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:8" ht="14" x14ac:dyDescent="0.3">
       <c r="B10" s="33" t="s">
         <v>37</v>
       </c>
@@ -4561,7 +4546,7 @@
         <v>2246761.8275050255</v>
       </c>
     </row>
-    <row r="11" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:8" ht="14" x14ac:dyDescent="0.3">
       <c r="B11" s="8" t="s">
         <v>182</v>
       </c>
@@ -4572,7 +4557,7 @@
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
     </row>
-    <row r="12" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:8" ht="14" x14ac:dyDescent="0.3">
       <c r="B12" s="33" t="s">
         <v>183</v>
       </c>
@@ -4600,7 +4585,7 @@
         <v>635467.67242428358</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:8" ht="14" x14ac:dyDescent="0.3">
       <c r="B13" s="33" t="s">
         <v>184</v>
       </c>
@@ -4628,7 +4613,7 @@
         <v>387797.24693922361</v>
       </c>
     </row>
-    <row r="14" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:8" ht="14" x14ac:dyDescent="0.3">
       <c r="B14" s="33" t="s">
         <v>185</v>
       </c>
@@ -4657,7 +4642,7 @@
         <v>1023264.9193635072</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:8" ht="14" x14ac:dyDescent="0.3">
       <c r="B15" s="33" t="s">
         <v>186</v>
       </c>
@@ -4685,7 +4670,7 @@
         <v>467818.90106953954</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:8" ht="14" x14ac:dyDescent="0.3">
       <c r="B16" s="33" t="s">
         <v>187</v>
       </c>
@@ -4714,7 +4699,7 @@
         <v>467818.90106953954</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:8" ht="14" x14ac:dyDescent="0.3">
       <c r="B17" s="22" t="s">
         <v>188</v>
       </c>
@@ -4725,7 +4710,7 @@
       <c r="G17" s="23"/>
       <c r="H17" s="23"/>
     </row>
-    <row r="18" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:8" ht="14" x14ac:dyDescent="0.3">
       <c r="B18" s="33" t="s">
         <v>189</v>
       </c>
@@ -4754,7 +4739,7 @@
         <v>555446.0182939677</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:8" ht="14" x14ac:dyDescent="0.3">
       <c r="B19" s="33" t="s">
         <v>98</v>
       </c>
@@ -4782,7 +4767,7 @@
         <v>10891.098397921072</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:8" ht="14" x14ac:dyDescent="0.3">
       <c r="B22" s="22" t="s">
         <v>190</v>
       </c>
@@ -4793,7 +4778,7 @@
       <c r="G22" s="23"/>
       <c r="H22" s="23"/>
     </row>
-    <row r="23" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:8" ht="14" x14ac:dyDescent="0.3">
       <c r="D23" s="25" t="s">
         <v>84</v>
       </c>
@@ -4810,12 +4795,12 @@
         <v>88</v>
       </c>
     </row>
-    <row r="24" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:8" ht="14" x14ac:dyDescent="0.3">
       <c r="B24" s="3" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="25" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:8" ht="14" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
         <v>82</v>
       </c>
@@ -4835,7 +4820,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:8" ht="14" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
         <v>119</v>
       </c>
@@ -4855,7 +4840,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:8" ht="14" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
         <v>120</v>
       </c>
@@ -4875,7 +4860,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:8" ht="14" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
         <v>121</v>
       </c>
@@ -4895,7 +4880,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="29" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:8" ht="14" x14ac:dyDescent="0.3">
       <c r="B29" s="4" t="s">
         <v>122</v>
       </c>
@@ -4915,12 +4900,12 @@
         <v>94</v>
       </c>
     </row>
-    <row r="31" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:8" ht="14" x14ac:dyDescent="0.3">
       <c r="B31" s="3" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="32" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:8" ht="14" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
         <v>82</v>
       </c>
@@ -4940,7 +4925,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:8" ht="14" x14ac:dyDescent="0.3">
       <c r="B33" s="4" t="s">
         <v>119</v>
       </c>
@@ -4960,7 +4945,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="34" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:8" ht="14" x14ac:dyDescent="0.3">
       <c r="B34" s="4" t="s">
         <v>120</v>
       </c>
@@ -4980,7 +4965,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:8" ht="14" x14ac:dyDescent="0.3">
       <c r="B35" s="4" t="s">
         <v>121</v>
       </c>
@@ -5000,7 +4985,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:8" ht="14" x14ac:dyDescent="0.3">
       <c r="B36" s="4" t="s">
         <v>122</v>
       </c>
@@ -5020,12 +5005,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="38" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:8" ht="14" x14ac:dyDescent="0.3">
       <c r="B38" s="3" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="39" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:8" ht="14" x14ac:dyDescent="0.3">
       <c r="B39" s="4" t="s">
         <v>82</v>
       </c>
@@ -5045,7 +5030,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:8" ht="14" x14ac:dyDescent="0.3">
       <c r="B40" s="4" t="s">
         <v>119</v>
       </c>
@@ -5065,7 +5050,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:8" ht="14" x14ac:dyDescent="0.3">
       <c r="B41" s="4" t="s">
         <v>120</v>
       </c>
@@ -5085,7 +5070,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:8" ht="14" x14ac:dyDescent="0.3">
       <c r="B42" s="4" t="s">
         <v>121</v>
       </c>
@@ -5105,7 +5090,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="43" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:8" ht="14" x14ac:dyDescent="0.3">
       <c r="B43" s="4" t="s">
         <v>122</v>
       </c>
@@ -5146,17 +5131,17 @@
     <col min="17" max="17" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:17" ht="18" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="3" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:17" ht="14" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="4" spans="2:17" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:17" ht="28" x14ac:dyDescent="0.3">
       <c r="B4" s="10" t="s">
         <v>3</v>
       </c>
@@ -5206,7 +5191,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="5" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:17" ht="14" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>4</v>
       </c>
@@ -5261,7 +5246,7 @@
         <v>1719296</v>
       </c>
     </row>
-    <row r="6" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:17" ht="14" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>211</v>
       </c>
@@ -5314,7 +5299,7 @@
         <v>4484266</v>
       </c>
     </row>
-    <row r="7" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:17" ht="14" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
         <v>213</v>
       </c>
@@ -5367,7 +5352,7 @@
         <v>6568369</v>
       </c>
     </row>
-    <row r="8" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:17" ht="14" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
         <v>215</v>
       </c>
@@ -5420,7 +5405,7 @@
         <v>5492689</v>
       </c>
     </row>
-    <row r="9" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:17" ht="14" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
         <v>217</v>
       </c>
@@ -5473,7 +5458,7 @@
         <v>2718743</v>
       </c>
     </row>
-    <row r="10" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:17" ht="14" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
         <v>219</v>
       </c>
@@ -5526,12 +5511,12 @@
         <v>3088566</v>
       </c>
     </row>
-    <row r="14" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:17" ht="14" x14ac:dyDescent="0.3">
       <c r="B14" s="3" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="15" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:17" ht="14" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
         <v>222</v>
       </c>
@@ -5560,7 +5545,7 @@
         <v>8.0790119375045627E-2</v>
       </c>
     </row>
-    <row r="16" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:17" ht="14" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
         <v>223</v>
       </c>
@@ -5589,7 +5574,7 @@
         <v>8.6039761757547517E-2</v>
       </c>
     </row>
-    <row r="17" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
         <v>224</v>
       </c>
@@ -5618,7 +5603,7 @@
         <v>9.0930823461409294E-2</v>
       </c>
     </row>
-    <row r="19" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B19" s="22" t="s">
         <v>225</v>
       </c>
@@ -5630,12 +5615,12 @@
       <c r="H19" s="23"/>
       <c r="I19" s="23"/>
     </row>
-    <row r="20" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B20" s="3" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="21" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
         <v>227</v>
       </c>
@@ -5643,7 +5628,7 @@
         <v>376184</v>
       </c>
     </row>
-    <row r="22" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B22" s="4" t="s">
         <v>228</v>
       </c>
@@ -5651,7 +5636,7 @@
         <v>164365</v>
       </c>
     </row>
-    <row r="23" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
         <v>229</v>
       </c>
@@ -5659,7 +5644,7 @@
         <v>1146309835</v>
       </c>
     </row>
-    <row r="24" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
         <v>71</v>
       </c>
@@ -5667,12 +5652,12 @@
         <v>367577</v>
       </c>
     </row>
-    <row r="26" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B26" s="3" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="27" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
         <v>231</v>
       </c>
@@ -5681,7 +5666,7 @@
         <v>4783</v>
       </c>
     </row>
-    <row r="28" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
         <v>232</v>
       </c>
@@ -5709,12 +5694,12 @@
     <col min="3" max="9" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:9" ht="18" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="3" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
         <v>234</v>
       </c>
@@ -5737,12 +5722,12 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="5" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="6" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B6" s="40" t="s">
         <v>238</v>
       </c>
@@ -5775,250 +5760,250 @@
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
       <c r="B7" s="39">
         <f>$C$3-0.015</f>
         <v>8.1473102956893473E-2</v>
       </c>
       <c r="C7" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B7)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B7)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B7)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B7)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B7)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+C$6)/($B7-C$6)/(1+$B7)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>1778</v>
+        <v>2075</v>
       </c>
       <c r="D7" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B7)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B7)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B7)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B7)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B7)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+D$6)/($B7-D$6)/(1+$B7)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>1825</v>
+        <v>2130</v>
       </c>
       <c r="E7" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B7)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B7)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B7)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B7)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B7)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+E$6)/($B7-E$6)/(1+$B7)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>1876</v>
+        <v>2189</v>
       </c>
       <c r="F7" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B7)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B7)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B7)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B7)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B7)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+F$6)/($B7-F$6)/(1+$B7)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>1930</v>
+        <v>2251</v>
       </c>
       <c r="G7" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B7)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B7)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B7)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B7)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B7)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+G$6)/($B7-G$6)/(1+$B7)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>1989</v>
+        <v>2319</v>
       </c>
       <c r="H7" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B7)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B7)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B7)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B7)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B7)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+H$6)/($B7-H$6)/(1+$B7)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>2051</v>
+        <v>2391</v>
       </c>
       <c r="I7" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B7)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B7)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B7)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B7)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B7)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+I$6)/($B7-I$6)/(1+$B7)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>2119</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>2469</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
       <c r="B8" s="39">
         <f>$C$3-0.01</f>
         <v>8.6473102956893477E-2</v>
       </c>
       <c r="C8" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B8)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B8)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B8)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B8)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B8)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+C$6)/($B8-C$6)/(1+$B8)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>1664</v>
+        <v>1945</v>
       </c>
       <c r="D8" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B8)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B8)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B8)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B8)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B8)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+D$6)/($B8-D$6)/(1+$B8)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>1706</v>
+        <v>1992</v>
       </c>
       <c r="E8" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B8)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B8)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B8)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B8)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B8)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+E$6)/($B8-E$6)/(1+$B8)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>1750</v>
+        <v>2043</v>
       </c>
       <c r="F8" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B8)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B8)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B8)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B8)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B8)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+F$6)/($B8-F$6)/(1+$B8)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>1797</v>
+        <v>2097</v>
       </c>
       <c r="G8" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B8)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B8)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B8)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B8)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B8)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+G$6)/($B8-G$6)/(1+$B8)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>1846</v>
+        <v>2155</v>
       </c>
       <c r="H8" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B8)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B8)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B8)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B8)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B8)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+H$6)/($B8-H$6)/(1+$B8)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>1900</v>
+        <v>2216</v>
       </c>
       <c r="I8" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B8)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B8)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B8)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B8)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B8)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+I$6)/($B8-I$6)/(1+$B8)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>1957</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>2282</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
       <c r="B9" s="39">
         <f>$C$3-0.005</f>
         <v>9.1473102956893468E-2</v>
       </c>
       <c r="C9" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B9)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B9)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B9)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B9)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B9)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+C$6)/($B9-C$6)/(1+$B9)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>1564</v>
+        <v>1829</v>
       </c>
       <c r="D9" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B9)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B9)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B9)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B9)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B9)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+D$6)/($B9-D$6)/(1+$B9)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>1600</v>
+        <v>1871</v>
       </c>
       <c r="E9" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B9)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B9)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B9)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B9)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B9)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+E$6)/($B9-E$6)/(1+$B9)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>1638</v>
+        <v>1915</v>
       </c>
       <c r="F9" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B9)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B9)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B9)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B9)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B9)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+F$6)/($B9-F$6)/(1+$B9)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>1679</v>
+        <v>1962</v>
       </c>
       <c r="G9" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B9)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B9)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B9)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B9)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B9)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+G$6)/($B9-G$6)/(1+$B9)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>1722</v>
+        <v>2012</v>
       </c>
       <c r="H9" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B9)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B9)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B9)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B9)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B9)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+H$6)/($B9-H$6)/(1+$B9)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>1768</v>
+        <v>2065</v>
       </c>
       <c r="I9" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B9)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B9)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B9)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B9)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B9)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+I$6)/($B9-I$6)/(1+$B9)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>1817</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>2121</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
       <c r="B10" s="39">
         <f>$C$3</f>
         <v>9.6473102956893472E-2</v>
       </c>
       <c r="C10" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B10)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B10)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B10)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B10)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B10)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+C$6)/($B10-C$6)/(1+$B10)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>1474</v>
+        <v>1725</v>
       </c>
       <c r="D10" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B10)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B10)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B10)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B10)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B10)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+D$6)/($B10-D$6)/(1+$B10)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>1506</v>
+        <v>1762</v>
       </c>
       <c r="E10" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B10)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B10)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B10)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B10)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B10)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+E$6)/($B10-E$6)/(1+$B10)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>1540</v>
+        <v>1801</v>
       </c>
       <c r="F10" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B10)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B10)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B10)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B10)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B10)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+F$6)/($B10-F$6)/(1+$B10)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>1575</v>
+        <v>1842</v>
       </c>
       <c r="G10" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B10)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B10)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B10)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B10)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B10)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+G$6)/($B10-G$6)/(1+$B10)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>1613</v>
+        <v>1885</v>
       </c>
       <c r="H10" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B10)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B10)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B10)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B10)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B10)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+H$6)/($B10-H$6)/(1+$B10)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>1653</v>
+        <v>1932</v>
       </c>
       <c r="I10" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B10)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B10)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B10)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B10)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B10)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+I$6)/($B10-I$6)/(1+$B10)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>1695</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1981</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
       <c r="B11" s="39">
         <f>$C$3+0.005</f>
         <v>0.10147310295689348</v>
       </c>
       <c r="C11" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B11)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B11)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B11)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B11)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B11)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+C$6)/($B11-C$6)/(1+$B11)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>1393</v>
+        <v>1632</v>
       </c>
       <c r="D11" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B11)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B11)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B11)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B11)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B11)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+D$6)/($B11-D$6)/(1+$B11)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>1421</v>
+        <v>1665</v>
       </c>
       <c r="E11" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B11)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B11)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B11)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B11)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B11)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+E$6)/($B11-E$6)/(1+$B11)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>1451</v>
+        <v>1699</v>
       </c>
       <c r="F11" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B11)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B11)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B11)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B11)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B11)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+F$6)/($B11-F$6)/(1+$B11)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>1482</v>
+        <v>1735</v>
       </c>
       <c r="G11" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B11)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B11)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B11)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B11)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B11)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+G$6)/($B11-G$6)/(1+$B11)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>1516</v>
+        <v>1773</v>
       </c>
       <c r="H11" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B11)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B11)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B11)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B11)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B11)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+H$6)/($B11-H$6)/(1+$B11)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>1551</v>
+        <v>1814</v>
       </c>
       <c r="I11" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B11)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B11)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B11)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B11)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B11)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+I$6)/($B11-I$6)/(1+$B11)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>1588</v>
-      </c>
-    </row>
-    <row r="12" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1857</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
       <c r="B12" s="39">
         <f>$C$3+0.01</f>
         <v>0.10647310295689347</v>
       </c>
       <c r="C12" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B12)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B12)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B12)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B12)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B12)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+C$6)/($B12-C$6)/(1+$B12)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>1320</v>
+        <v>1548</v>
       </c>
       <c r="D12" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B12)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B12)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B12)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B12)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B12)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+D$6)/($B12-D$6)/(1+$B12)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>1345</v>
+        <v>1577</v>
       </c>
       <c r="E12" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B12)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B12)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B12)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B12)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B12)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+E$6)/($B12-E$6)/(1+$B12)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>1372</v>
+        <v>1608</v>
       </c>
       <c r="F12" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B12)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B12)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B12)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B12)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B12)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+F$6)/($B12-F$6)/(1+$B12)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>1399</v>
+        <v>1640</v>
       </c>
       <c r="G12" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B12)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B12)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B12)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B12)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B12)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+G$6)/($B12-G$6)/(1+$B12)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>1429</v>
+        <v>1673</v>
       </c>
       <c r="H12" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B12)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B12)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B12)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B12)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B12)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+H$6)/($B12-H$6)/(1+$B12)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>1460</v>
+        <v>1709</v>
       </c>
       <c r="I12" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B12)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B12)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B12)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B12)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B12)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+I$6)/($B12-I$6)/(1+$B12)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>1492</v>
-      </c>
-    </row>
-    <row r="13" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1746</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
       <c r="B13" s="39">
         <f>$C$3+0.015</f>
         <v>0.11147310295689347</v>
       </c>
       <c r="C13" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B13)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B13)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B13)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B13)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B13)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+C$6)/($B13-C$6)/(1+$B13)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>1254</v>
+        <v>1472</v>
       </c>
       <c r="D13" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B13)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B13)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B13)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B13)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B13)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+D$6)/($B13-D$6)/(1+$B13)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>1276</v>
+        <v>1498</v>
       </c>
       <c r="E13" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B13)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B13)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B13)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B13)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B13)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+E$6)/($B13-E$6)/(1+$B13)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>1300</v>
+        <v>1525</v>
       </c>
       <c r="F13" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B13)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B13)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B13)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B13)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B13)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+F$6)/($B13-F$6)/(1+$B13)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>1325</v>
+        <v>1553</v>
       </c>
       <c r="G13" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B13)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B13)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B13)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B13)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B13)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+G$6)/($B13-G$6)/(1+$B13)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>1351</v>
+        <v>1583</v>
       </c>
       <c r="H13" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B13)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B13)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B13)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B13)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B13)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+H$6)/($B13-H$6)/(1+$B13)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>1378</v>
+        <v>1615</v>
       </c>
       <c r="I13" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B13)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B13)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B13)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B13)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B13)^('DCF Model'!C19+4)+'DCF Model'!G45*(1+I$6)/($B13-I$6)/(1+$B13)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>1407</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1648</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B16" s="3" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="17" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B17" s="40" t="s">
         <v>240</v>
       </c>
@@ -6051,245 +6036,245 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="18" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
       <c r="B18" s="39">
         <f>$C$3-0.015</f>
         <v>8.1473102956893473E-2</v>
       </c>
       <c r="C18" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B18)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B18)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B18)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B18)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B18)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*C$17/(1+$B18)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>3561</v>
+        <v>3654</v>
       </c>
       <c r="D18" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B18)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B18)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B18)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B18)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B18)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*D$17/(1+$B18)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>3810</v>
+        <v>3902</v>
       </c>
       <c r="E18" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B18)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B18)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B18)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B18)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B18)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*E$17/(1+$B18)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>4058</v>
+        <v>4151</v>
       </c>
       <c r="F18" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B18)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B18)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B18)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B18)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B18)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*F$17/(1+$B18)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>4307</v>
+        <v>4400</v>
       </c>
       <c r="G18" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B18)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B18)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B18)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B18)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B18)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*G$17/(1+$B18)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>4555</v>
+        <v>4648</v>
       </c>
       <c r="H18" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B18)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B18)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B18)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B18)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B18)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*H$17/(1+$B18)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>4804</v>
+        <v>4897</v>
       </c>
       <c r="I18" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B18)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B18)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B18)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B18)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B18)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*I$17/(1+$B18)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>5052</v>
-      </c>
-    </row>
-    <row r="19" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>5145</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
       <c r="B19" s="39">
         <f>$C$3-0.01</f>
         <v>8.6473102956893477E-2</v>
       </c>
       <c r="C19" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B19)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B19)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B19)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B19)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B19)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*C$17/(1+$B19)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>3490</v>
+        <v>3581</v>
       </c>
       <c r="D19" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B19)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B19)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B19)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B19)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B19)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*D$17/(1+$B19)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>3733</v>
+        <v>3825</v>
       </c>
       <c r="E19" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B19)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B19)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B19)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B19)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B19)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*E$17/(1+$B19)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>3977</v>
+        <v>4068</v>
       </c>
       <c r="F19" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B19)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B19)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B19)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B19)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B19)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*F$17/(1+$B19)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>4220</v>
+        <v>4312</v>
       </c>
       <c r="G19" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B19)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B19)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B19)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B19)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B19)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*G$17/(1+$B19)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>4464</v>
+        <v>4555</v>
       </c>
       <c r="H19" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B19)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B19)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B19)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B19)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B19)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*H$17/(1+$B19)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>4707</v>
+        <v>4799</v>
       </c>
       <c r="I19" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B19)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B19)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B19)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B19)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B19)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*I$17/(1+$B19)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>4951</v>
-      </c>
-    </row>
-    <row r="20" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>5043</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
       <c r="B20" s="39">
         <f>$C$3-0.005</f>
         <v>9.1473102956893468E-2</v>
       </c>
       <c r="C20" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B20)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B20)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B20)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B20)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B20)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*C$17/(1+$B20)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>3420</v>
+        <v>3511</v>
       </c>
       <c r="D20" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B20)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B20)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B20)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B20)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B20)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*D$17/(1+$B20)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>3659</v>
+        <v>3749</v>
       </c>
       <c r="E20" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B20)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B20)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B20)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B20)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B20)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*E$17/(1+$B20)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>3897</v>
+        <v>3988</v>
       </c>
       <c r="F20" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B20)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B20)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B20)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B20)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B20)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*F$17/(1+$B20)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>4136</v>
+        <v>4227</v>
       </c>
       <c r="G20" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B20)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B20)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B20)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B20)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B20)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*G$17/(1+$B20)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>4374</v>
+        <v>4465</v>
       </c>
       <c r="H20" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B20)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B20)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B20)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B20)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B20)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*H$17/(1+$B20)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>4613</v>
+        <v>4704</v>
       </c>
       <c r="I20" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B20)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B20)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B20)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B20)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B20)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*I$17/(1+$B20)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>4851</v>
-      </c>
-    </row>
-    <row r="21" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4942</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
       <c r="B21" s="39">
         <f>$C$3</f>
         <v>9.6473102956893472E-2</v>
       </c>
       <c r="C21" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B21)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B21)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B21)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B21)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B21)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*C$17/(1+$B21)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>3352</v>
+        <v>3442</v>
       </c>
       <c r="D21" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B21)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B21)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B21)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B21)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B21)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*D$17/(1+$B21)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>3586</v>
+        <v>3676</v>
       </c>
       <c r="E21" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B21)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B21)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B21)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B21)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B21)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*E$17/(1+$B21)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>3820</v>
+        <v>3909</v>
       </c>
       <c r="F21" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B21)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B21)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B21)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B21)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B21)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*F$17/(1+$B21)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>4053</v>
+        <v>4143</v>
       </c>
       <c r="G21" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B21)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B21)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B21)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B21)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B21)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*G$17/(1+$B21)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>4287</v>
+        <v>4377</v>
       </c>
       <c r="H21" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B21)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B21)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B21)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B21)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B21)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*H$17/(1+$B21)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>4521</v>
+        <v>4611</v>
       </c>
       <c r="I21" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B21)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B21)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B21)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B21)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B21)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*I$17/(1+$B21)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>4754</v>
-      </c>
-    </row>
-    <row r="22" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4844</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
       <c r="B22" s="39">
         <f>$C$3+0.005</f>
         <v>0.10147310295689348</v>
       </c>
       <c r="C22" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B22)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B22)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B22)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B22)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B22)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*C$17/(1+$B22)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>3286</v>
+        <v>3375</v>
       </c>
       <c r="D22" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B22)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B22)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B22)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B22)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B22)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*D$17/(1+$B22)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>3515</v>
+        <v>3604</v>
       </c>
       <c r="E22" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B22)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B22)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B22)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B22)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B22)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*E$17/(1+$B22)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>3744</v>
+        <v>3833</v>
       </c>
       <c r="F22" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B22)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B22)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B22)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B22)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B22)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*F$17/(1+$B22)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>3973</v>
+        <v>4062</v>
       </c>
       <c r="G22" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B22)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B22)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B22)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B22)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B22)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*G$17/(1+$B22)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>4202</v>
+        <v>4291</v>
       </c>
       <c r="H22" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B22)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B22)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B22)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B22)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B22)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*H$17/(1+$B22)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>4431</v>
+        <v>4520</v>
       </c>
       <c r="I22" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B22)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B22)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B22)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B22)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B22)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*I$17/(1+$B22)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>4660</v>
-      </c>
-    </row>
-    <row r="23" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4749</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
       <c r="B23" s="39">
         <f>$C$3+0.01</f>
         <v>0.10647310295689347</v>
       </c>
       <c r="C23" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B23)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B23)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B23)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B23)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B23)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*C$17/(1+$B23)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>3222</v>
+        <v>3309</v>
       </c>
       <c r="D23" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B23)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B23)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B23)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B23)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B23)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*D$17/(1+$B23)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>3446</v>
+        <v>3534</v>
       </c>
       <c r="E23" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B23)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B23)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B23)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B23)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B23)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*E$17/(1+$B23)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>3670</v>
+        <v>3758</v>
       </c>
       <c r="F23" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B23)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B23)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B23)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B23)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B23)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*F$17/(1+$B23)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>3895</v>
+        <v>3982</v>
       </c>
       <c r="G23" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B23)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B23)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B23)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B23)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B23)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*G$17/(1+$B23)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>4119</v>
+        <v>4207</v>
       </c>
       <c r="H23" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B23)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B23)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B23)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B23)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B23)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*H$17/(1+$B23)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>4343</v>
+        <v>4431</v>
       </c>
       <c r="I23" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B23)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B23)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B23)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B23)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B23)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*I$17/(1+$B23)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>4567</v>
-      </c>
-    </row>
-    <row r="24" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4655</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
       <c r="B24" s="39">
         <f>$C$3+0.015</f>
         <v>0.11147310295689347</v>
       </c>
       <c r="C24" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B24)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B24)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B24)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B24)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B24)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*C$17/(1+$B24)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>3159</v>
+        <v>3245</v>
       </c>
       <c r="D24" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B24)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B24)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B24)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B24)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B24)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*D$17/(1+$B24)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>3378</v>
+        <v>3465</v>
       </c>
       <c r="E24" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B24)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B24)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B24)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B24)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B24)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*E$17/(1+$B24)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>3598</v>
+        <v>3685</v>
       </c>
       <c r="F24" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B24)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B24)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B24)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B24)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B24)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*F$17/(1+$B24)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>3818</v>
+        <v>3905</v>
       </c>
       <c r="G24" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B24)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B24)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B24)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B24)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B24)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*G$17/(1+$B24)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>4038</v>
+        <v>4125</v>
       </c>
       <c r="H24" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B24)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B24)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B24)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B24)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B24)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*H$17/(1+$B24)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>4258</v>
+        <v>4345</v>
       </c>
       <c r="I24" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B24)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B24)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B24)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B24)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B24)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*I$17/(1+$B24)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>4477</v>
-      </c>
-    </row>
-    <row r="26" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+        <v>4564</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B26" s="45" t="s">
         <v>241</v>
       </c>
@@ -6326,12 +6311,12 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:7" ht="18" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="4" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B4" s="10" t="s">
         <v>243</v>
       </c>
@@ -6391,434 +6376,414 @@
         <v>258</v>
       </c>
     </row>
-    <row r="7" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" t="s">
-        <v>249</v>
-      </c>
-      <c r="C7" t="s">
+    <row r="12" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+      <c r="B12" s="8" t="s">
         <v>259</v>
       </c>
-      <c r="D7" t="s">
+    </row>
+    <row r="13" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+      <c r="B13" s="10" t="s">
         <v>260</v>
       </c>
-      <c r="E7" t="s">
+      <c r="C13" s="10" t="s">
         <v>261</v>
       </c>
-      <c r="F7" t="s">
+    </row>
+    <row r="14" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+      <c r="B14" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="G7" t="s">
+      <c r="C14" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="12" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="8" t="s">
+    <row r="15" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+      <c r="B15" s="4" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="13" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="10" t="s">
+      <c r="C15" t="s">
         <v>265</v>
       </c>
-      <c r="C13" s="10" t="s">
+    </row>
+    <row r="16" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+      <c r="B16" s="4" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="14" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="4" t="s">
+      <c r="C16" t="s">
         <v>267</v>
       </c>
-      <c r="C14" t="s">
+    </row>
+    <row r="17" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+      <c r="B17" s="4" t="s">
         <v>268</v>
       </c>
-    </row>
-    <row r="15" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="4" t="s">
+      <c r="C17" t="s">
         <v>269</v>
       </c>
-      <c r="C15" t="s">
+    </row>
+    <row r="18" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+      <c r="B18" s="4" t="s">
         <v>270</v>
       </c>
-    </row>
-    <row r="16" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="4" t="s">
+      <c r="C18" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+      <c r="B19" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C19" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="17" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="4" t="s">
+    <row r="20" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+      <c r="B20" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C20" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="18" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="4" t="s">
+    <row r="21" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+      <c r="B21" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="C18" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="19" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="4" t="s">
+      <c r="C21" t="s">
         <v>276</v>
       </c>
-      <c r="C19" t="s">
+    </row>
+    <row r="22" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+      <c r="B22" s="4" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="20" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="4" t="s">
+      <c r="C22" t="s">
         <v>278</v>
       </c>
-      <c r="C20" t="s">
+    </row>
+    <row r="23" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+      <c r="B23" s="4" t="s">
         <v>279</v>
-      </c>
-    </row>
-    <row r="21" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="C21" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="22" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="4" t="s">
-        <v>282</v>
-      </c>
-      <c r="C22" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="23" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="4" t="s">
-        <v>284</v>
       </c>
       <c r="C23" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:3" ht="14" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="C24" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:3" ht="14" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="C25" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="26" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:3" ht="14" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="C26" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+      <c r="B27" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="C27" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+      <c r="B28" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="C28" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+      <c r="B29" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="C29" t="s">
         <v>287</v>
       </c>
-      <c r="C26" t="s">
+    </row>
+    <row r="30" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+      <c r="B30" s="4" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="27" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="4" t="s">
+      <c r="C30" t="s">
         <v>289</v>
       </c>
-      <c r="C27" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="28" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="4" t="s">
+    </row>
+    <row r="31" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+      <c r="B31" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="C28" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="29" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="4" t="s">
+      <c r="C31" t="s">
         <v>291</v>
       </c>
-      <c r="C29" t="s">
+    </row>
+    <row r="32" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+      <c r="B32" s="4" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="30" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="4" t="s">
+      <c r="C32" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+      <c r="B33" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C33" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+      <c r="B34" s="4" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="31" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="4" t="s">
+      <c r="C34" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="35" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+      <c r="B35" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C35" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="32" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="4" t="s">
+    <row r="36" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+      <c r="B36" s="4" t="s">
         <v>297</v>
       </c>
-      <c r="C32" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="33" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="4" t="s">
+      <c r="C36" t="s">
         <v>298</v>
       </c>
-      <c r="C33" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="34" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="4" t="s">
+    </row>
+    <row r="37" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+      <c r="B37" s="4" t="s">
         <v>299</v>
       </c>
-      <c r="C34" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="35" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="4" t="s">
+      <c r="C37" t="s">
         <v>300</v>
       </c>
-      <c r="C35" t="s">
+    </row>
+    <row r="38" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+      <c r="B38" s="4" t="s">
         <v>301</v>
       </c>
-    </row>
-    <row r="36" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="4" t="s">
+      <c r="C38" t="s">
         <v>302</v>
       </c>
-      <c r="C36" t="s">
+    </row>
+    <row r="39" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+      <c r="B39" s="4" t="s">
         <v>303</v>
       </c>
-    </row>
-    <row r="37" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="4" t="s">
+      <c r="C39" t="s">
         <v>304</v>
       </c>
-      <c r="C37" t="s">
+    </row>
+    <row r="40" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+      <c r="B40" s="4" t="s">
         <v>305</v>
       </c>
-    </row>
-    <row r="38" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="4" t="s">
+      <c r="C40" t="s">
         <v>306</v>
       </c>
-      <c r="C38" t="s">
+    </row>
+    <row r="41" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+      <c r="B41" s="4" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="39" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="4" t="s">
+      <c r="C41" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="42" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+      <c r="B42" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C42" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="40" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="4" t="s">
+    <row r="43" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+      <c r="B43" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C43" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="41" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="4" t="s">
+    <row r="44" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+      <c r="B44" s="4" t="s">
         <v>312</v>
       </c>
-      <c r="C41" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="42" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="4" t="s">
+      <c r="C44" t="s">
         <v>313</v>
       </c>
-      <c r="C42" t="s">
+    </row>
+    <row r="45" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+      <c r="B45" s="4" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="43" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B43" s="4" t="s">
+      <c r="C45" t="s">
         <v>315</v>
       </c>
-      <c r="C43" t="s">
+    </row>
+    <row r="46" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+      <c r="B46" s="4" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="44" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="4" t="s">
+      <c r="C46" t="s">
         <v>317</v>
       </c>
-      <c r="C44" t="s">
+    </row>
+    <row r="47" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+      <c r="B47" s="4" t="s">
         <v>318</v>
       </c>
-    </row>
-    <row r="45" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B45" s="4" t="s">
+      <c r="C47" t="s">
         <v>319</v>
       </c>
-      <c r="C45" t="s">
+    </row>
+    <row r="48" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+      <c r="B48" s="4" t="s">
         <v>320</v>
       </c>
-    </row>
-    <row r="46" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="4" t="s">
+      <c r="C48" t="s">
         <v>321</v>
       </c>
-      <c r="C46" t="s">
+    </row>
+    <row r="49" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+      <c r="B49" s="4" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="47" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B47" s="4" t="s">
+      <c r="C49" t="s">
         <v>323</v>
       </c>
-      <c r="C47" t="s">
+    </row>
+    <row r="50" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+      <c r="B50" s="4" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="48" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B48" s="4" t="s">
+      <c r="C50" t="s">
         <v>325</v>
       </c>
-      <c r="C48" t="s">
+    </row>
+    <row r="51" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+      <c r="B51" s="4" t="s">
         <v>326</v>
       </c>
-    </row>
-    <row r="49" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="4" t="s">
+      <c r="C51" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="52" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+      <c r="B52" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C52" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="50" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="4" t="s">
+    <row r="53" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+      <c r="B53" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C53" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="51" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B51" s="4" t="s">
+    <row r="54" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+      <c r="B54" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="C51" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="52" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="4" t="s">
+      <c r="C54" t="s">
         <v>332</v>
       </c>
-      <c r="C52" t="s">
+    </row>
+    <row r="55" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+      <c r="B55" s="4" t="s">
         <v>333</v>
       </c>
-    </row>
-    <row r="53" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B53" s="4" t="s">
+      <c r="C55" t="s">
         <v>334</v>
       </c>
-      <c r="C53" t="s">
+    </row>
+    <row r="56" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+      <c r="B56" s="4" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="54" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B54" s="4" t="s">
+      <c r="C56" t="s">
         <v>336</v>
       </c>
-      <c r="C54" t="s">
+    </row>
+    <row r="57" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+      <c r="B57" s="4" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="55" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="4" t="s">
+      <c r="C57" t="s">
         <v>338</v>
       </c>
-      <c r="C55" t="s">
+    </row>
+    <row r="58" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+      <c r="B58" s="4" t="s">
         <v>339</v>
       </c>
-    </row>
-    <row r="56" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B56" s="4" t="s">
+      <c r="C58" t="s">
         <v>340</v>
       </c>
-      <c r="C56" t="s">
+    </row>
+    <row r="59" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+      <c r="B59" s="4" t="s">
         <v>341</v>
       </c>
-    </row>
-    <row r="57" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="4" t="s">
+      <c r="C59" t="s">
         <v>342</v>
       </c>
-      <c r="C57" t="s">
+    </row>
+    <row r="60" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+      <c r="B60" s="4" t="s">
         <v>343</v>
       </c>
-    </row>
-    <row r="58" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="4" t="s">
+      <c r="C60" t="s">
         <v>344</v>
       </c>
-      <c r="C58" t="s">
+    </row>
+    <row r="61" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+      <c r="B61" s="4" t="s">
         <v>345</v>
       </c>
-    </row>
-    <row r="59" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B59" s="4" t="s">
+      <c r="C61" t="s">
         <v>346</v>
       </c>
-      <c r="C59" t="s">
+    </row>
+    <row r="62" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+      <c r="B62" s="4" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="60" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="4" t="s">
+      <c r="C62" t="s">
         <v>348</v>
       </c>
-      <c r="C60" t="s">
+    </row>
+    <row r="63" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+      <c r="B63" s="4" t="s">
         <v>349</v>
-      </c>
-    </row>
-    <row r="61" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B61" s="4" t="s">
-        <v>350</v>
-      </c>
-      <c r="C61" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="62" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="4" t="s">
-        <v>352</v>
-      </c>
-      <c r="C62" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="63" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B63" s="4" t="s">
-        <v>354</v>
       </c>
       <c r="C63" t="s">
         <v>210</v>
